--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,231 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125844117</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klia 1:9, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>435048</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6480966</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frösve</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125844103</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klia 1:9, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>435148</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6480710</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frösve</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Varav en planta uppkrafsad av vildsvin eller rådjur</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125844117</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,117 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128516531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Källehagens sandbarrskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>435136</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6480675</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frösve</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Dolph Lundgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Dolph Lundgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +1035,12 @@
       <c r="E5" t="n">
         <v>5449</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128516531</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104120931</v>
+        <v>104120879</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435052</v>
+        <v>435071</v>
       </c>
       <c r="R2" t="n">
-        <v>6480951</v>
+        <v>6480921</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,60 +792,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125844117</v>
+        <v>104120931</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klia 1:9, Vg</t>
+          <t>Skövde, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435048</v>
+        <v>435052</v>
       </c>
       <c r="R3" t="n">
-        <v>6480966</v>
+        <v>6480951</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,19 +891,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hannes Byström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hannes Byström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -910,7 +912,7 @@
         <v>125844103</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,48 +1024,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128516531</v>
+        <v>125844117</v>
       </c>
       <c r="B5" t="n">
-        <v>92840</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källehagens sandbarrskogar, Vg</t>
+          <t>Klia 1:9, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435136</v>
+        <v>435048</v>
       </c>
       <c r="R5" t="n">
-        <v>6480675</v>
+        <v>6480966</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,12 +1101,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,23 +1115,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dolph Lundgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dolph Lundgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 22268-2025 artfynd.xlsx
+++ b/artfynd/A 22268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120879</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104120931</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,8 +1151,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125844117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>